--- a/results/0916-all/晋陕甘黄土丘陵沟壑牧林农区/tech_selected_summary.xlsx
+++ b/results/0916-all/晋陕甘黄土丘陵沟壑牧林农区/tech_selected_summary.xlsx
@@ -178,172 +178,172 @@
     <t>子洲县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 1631.28</t>
+    <t>1631.28</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -481,28 +481,28 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 116007819.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 74501.14</t>
+    <t>116007819.97</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>74501.14</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 61158761.92</t>
+    <t>61158761.92</t>
   </si>
   <si>
     <t>Mixture additives _beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 94536.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 1335093.62</t>
+    <t>94536.00</t>
+  </si>
+  <si>
+    <t>1335093.62</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -547,28 +547,28 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 165541492.92</t>
+    <t>165541492.92</t>
   </si>
   <si>
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 1909158.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 4316522.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 2019377.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 3012948.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 192803.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 2491475.38</t>
+    <t>1909158.03</t>
+  </si>
+  <si>
+    <t>4316522.52</t>
+  </si>
+  <si>
+    <t>2019377.09</t>
+  </si>
+  <si>
+    <t>3012948.78</t>
+  </si>
+  <si>
+    <t>192803.20</t>
+  </si>
+  <si>
+    <t>2491475.38</t>
   </si>
 </sst>
 </file>
